--- a/tests/reference_data/test_scenario_flowsolver.xlsx
+++ b/tests/reference_data/test_scenario_flowsolver.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\PythonProjects\aiphoria\tests\reference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5694ACB1-1FCF-46C8-92A4-939D474CA29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E380E1-7B11-4CAD-8B6D-B39CD6F0AADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6435" yWindow="1815" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
+    <workbookView xWindow="-25635" yWindow="2265" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="11" r:id="rId1"/>
@@ -912,7 +912,82 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="20">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -1900,42 +1975,42 @@
   </sheetData>
   <autoFilter ref="B6:E6" xr:uid="{89FFA668-DA1A-459B-BD42-D0D7F7709F0D}"/>
   <conditionalFormatting sqref="C15:C16">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="notEqual">
+    <cfRule type="cellIs" dxfId="16" priority="12" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:C22">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="notEqual">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="notEqual">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C29">
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="notEqual">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C37:C38">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="notEqual">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3013,8 +3088,8 @@
       <c r="J2" t="s">
         <v>99</v>
       </c>
-      <c r="K2" t="b">
-        <v>0</v>
+      <c r="K2" s="24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -3045,11 +3120,32 @@
       <c r="J3" t="s">
         <v>99</v>
       </c>
-      <c r="K3" t="b">
-        <v>0</v>
+      <c r="K3" s="24" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="K2">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="notEqual">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="notEqual">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3" xr:uid="{EBE1F62D-CE34-4E37-A77A-792429DBCCFD}">
+      <formula1>Boolean</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
